--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://fsi.taxjustice.net/</t>
+          <t>https://fsi.taxjustice.net/full-list/</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:38:25+00:00</t>
+          <t>2026-10-24T09:10:22+00:00</t>
         </is>
       </c>
     </row>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>2018.073758229713</v>
+        <v>2029.164280935892</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>68.566</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5.662174431428257</v>
+        <v>24.9443560838699</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1397.702717520003</v>
+        <v>1220.390210041198</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>74.86699999999999</v>
+        <v>71.99199999999999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3.921579455461468</v>
+        <v>3.4989520907402</v>
       </c>
     </row>
     <row r="4">
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1227.739466421772</v>
+        <v>1082.37977938999</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>67.8115</v>
+        <v>64.5615</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3.444708096956204</v>
+        <v>6.5069355070591</v>
       </c>
     </row>
     <row r="5">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1111.291401828365</v>
+        <v>1021.526528380776</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>69.61601724137931</v>
+        <v>67.77549999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3.117986017923528</v>
+        <v>3.53259928524494</v>
       </c>
     </row>
     <row r="6">
@@ -678,22 +678,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>816.8379667550212</v>
+        <v>719.5167215733142</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>55.54</v>
+        <v>79.20016666666666</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.291828547454737</v>
+        <v>0.303800031542778</v>
       </c>
     </row>
     <row r="7">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>771.7358481647575</v>
+        <v>685.7227721303967</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>59.11900000000001</v>
+        <v>56.86900000000001</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2.165284083138896</v>
+        <v>5.18281124532223</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>715.1347693002016</v>
+        <v>651.2660127511164</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>62.4105</v>
+        <v>51.54</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2.006476616250631</v>
+        <v>10.7640452682972</v>
       </c>
     </row>
     <row r="9">
@@ -750,22 +750,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>671.0526228703367</v>
+        <v>559.7400908632524</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>68.9585</v>
+        <v>57.84400000000001</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1.882793920620808</v>
+        <v>2.4189917370677</v>
       </c>
     </row>
     <row r="10">
@@ -774,22 +774,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Guernsey</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>GG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>667.5662299171173</v>
+        <v>537.8121860432623</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>75.41499999999999</v>
+        <v>59.075</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1.873012035812521</v>
+        <v>1.77524518221617</v>
       </c>
     </row>
     <row r="11">
@@ -798,22 +798,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guernsey</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>GG</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>660.23727327138</v>
+        <v>537.6098578004126</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.825</v>
+        <v>70.78999999999999</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1.852448946500591</v>
+        <v>0.348060275427997</v>
       </c>
     </row>
     <row r="12">
@@ -822,22 +822,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>639.4640061939583</v>
+        <v>530.5675390967302</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>68.68584482758621</v>
+        <v>58.0825</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1.79416472312999</v>
+        <v>1.98524594306946</v>
       </c>
     </row>
     <row r="13">
@@ -846,22 +846,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>619.5405564044128</v>
+        <v>525.4278195923393</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>69.73896551724138</v>
+        <v>63.688</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1.738264859448512</v>
+        <v>0.8414352312684059</v>
       </c>
     </row>
     <row r="14">
@@ -870,22 +870,22 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>617.3690951910476</v>
+        <v>513.2570645020336</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78.86970689655172</v>
+        <v>65.2085</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.73217232090228</v>
+        <v>0.634259404614568</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>600.1109753923687</v>
+        <v>510.2579170374322</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>57.1015</v>
+        <v>66.6075</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1.683750659275637</v>
+        <v>0.514826690778136</v>
       </c>
     </row>
     <row r="16">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>592.7123428039999</v>
+        <v>472.5215364948238</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>78.3971724137931</v>
+        <v>73.11699999999999</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1.662992077931147</v>
+        <v>0.176644267048687</v>
       </c>
     </row>
     <row r="17">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>562.8439446350901</v>
+        <v>470.6061465178863</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>71.52346551724138</v>
+        <v>69.98150000000001</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.579189352817633</v>
+        <v>0.258894939906895</v>
       </c>
     </row>
     <row r="18">
@@ -966,22 +966,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>515.9738323556571</v>
+        <v>451.5840591726225</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>63.6515</v>
+        <v>43.816</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1.447684371761055</v>
+        <v>15.4711022973061</v>
       </c>
     </row>
     <row r="19">
@@ -990,22 +990,22 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Cayman Islands</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>506.3680247454379</v>
+        <v>444.8382759667423</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>58.0825</v>
+        <v>69.85633333333334</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1.420733048489544</v>
+        <v>0.222205277532339</v>
       </c>
     </row>
     <row r="20">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>498.3877434635596</v>
+        <v>424.9374833155096</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>73.31394827586207</v>
+        <v>69.24316666666667</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1.398342516703681</v>
+        <v>0.209692469798028</v>
       </c>
     </row>
     <row r="21">
@@ -1038,22 +1038,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>485.9761450993636</v>
+        <v>423.5629015510869</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>44.816</v>
+        <v>59.8855</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1.363518896097983</v>
+        <v>0.7671117316931489</v>
       </c>
     </row>
     <row r="22">
@@ -1062,22 +1062,22 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Jersey</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>455.3285215681374</v>
+        <v>423.0509883157104</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>51.73049999999999</v>
+        <v>62.573</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1.277529873330662</v>
+        <v>0.514867343008518</v>
       </c>
     </row>
     <row r="23">
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>450.8799213217593</v>
+        <v>421.5316875530311</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>70.70581034482758</v>
+        <v>50.3515</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1.265048292581709</v>
+        <v>3.60063388943672</v>
       </c>
     </row>
     <row r="24">
@@ -1110,22 +1110,22 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Jersey</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>JE</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>425.1870916497552</v>
+        <v>420.5270573494992</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>63.823</v>
+        <v>66.93350000000001</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.192961094258751</v>
+        <v>0.275797303766012</v>
       </c>
     </row>
     <row r="25">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>405.7805814215348</v>
+        <v>390.2635462812211</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>56.1991551724138</v>
+        <v>74.541</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.138511624525854</v>
+        <v>0.08365983958356099</v>
       </c>
     </row>
     <row r="26">
@@ -1158,22 +1158,22 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>403.1651580607158</v>
+        <v>386.6695593360644</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>63.46712068965518</v>
+        <v>56.17616666666667</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1.131173447107612</v>
+        <v>1.03765036910772</v>
       </c>
     </row>
     <row r="27">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>389.7412164732856</v>
+        <v>377.3655948966567</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>54.371</v>
+        <v>53.371</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.093509462570193</v>
+        <v>1.52946254238486</v>
       </c>
     </row>
     <row r="28">
@@ -1206,22 +1206,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Macao</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>386.4417118518345</v>
+        <v>368.6640470830673</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>66.32420689655171</v>
+        <v>48.4805</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1.084251936363446</v>
+        <v>3.3867921680212</v>
       </c>
     </row>
     <row r="29">
@@ -1230,22 +1230,22 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>380.0837253375141</v>
+        <v>332.3902948992915</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>69.68781034482758</v>
+        <v>59.54183333333334</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1.066413129169238</v>
+        <v>0.390431797131896</v>
       </c>
     </row>
     <row r="30">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>365.135931280856</v>
+        <v>315.0226463538268</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>59.49260344827586</v>
+        <v>57.637</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1.024473622761846</v>
+        <v>0.445361854508519</v>
       </c>
     </row>
     <row r="31">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DZ</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>364.4349502418183</v>
+        <v>303.6923873066501</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>53.3785</v>
+        <v>73.75</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.022506857721684</v>
+        <v>0.043395379907452</v>
       </c>
     </row>
     <row r="32">
@@ -1302,22 +1302,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>364.410059120081</v>
+        <v>295.9411277237157</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>72.68970689655171</v>
+        <v>67.5085</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1.022437019901091</v>
+        <v>0.088999967556447</v>
       </c>
     </row>
     <row r="33">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>363.3174518054951</v>
+        <v>291.2947734943245</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>75.38843103448275</v>
+        <v>70.70883333333333</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.019371456427501</v>
+        <v>0.055941619211808</v>
       </c>
     </row>
     <row r="34">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>350.9939249269248</v>
+        <v>289.3413874204643</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>76.7</v>
+        <v>61.1835</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.9847949408208215</v>
+        <v>0.201614992693067</v>
       </c>
     </row>
     <row r="35">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>341.848231405488</v>
+        <v>285.6093486002226</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>54.60850000000001</v>
+        <v>63.088</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.9591345744424465</v>
+        <v>0.147162249777466</v>
       </c>
     </row>
     <row r="36">
@@ -1398,22 +1398,22 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>321.791054862584</v>
+        <v>280.788527378634</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>59.66799999999999</v>
+        <v>64.48983333333334</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.9028595093092987</v>
+        <v>0.114740512799472</v>
       </c>
     </row>
     <row r="37">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>314.6841293208248</v>
+        <v>276.3186187295555</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>66.94529310344828</v>
+        <v>64.03283333333334</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.8829193798048581</v>
+        <v>0.116575148422271</v>
       </c>
     </row>
     <row r="38">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Macao</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>307.930270978079</v>
+        <v>275.6542521546351</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>73.15779310344828</v>
+        <v>62.52966666666666</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.8639698622930058</v>
+        <v>0.143324048258364</v>
       </c>
     </row>
     <row r="39">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>306.5739699335887</v>
+        <v>270.6995177012362</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>65.55941379310346</v>
+        <v>49.6285</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.8601644448427691</v>
+        <v>1.08613073825836</v>
       </c>
     </row>
     <row r="40">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>303.4215522173392</v>
+        <v>270.4263847893836</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>70.19358620689654</v>
+        <v>71.5065</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.8513196050952927</v>
+        <v>0.040461082244292</v>
       </c>
     </row>
     <row r="41">
@@ -1518,22 +1518,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>287.9835860169075</v>
+        <v>270.4245690628497</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>75.42749999999999</v>
+        <v>77.55850000000001</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.8080048069434064</v>
+        <v>0.019474836881273</v>
       </c>
     </row>
     <row r="42">
@@ -1542,22 +1542,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>284.5742834946308</v>
+        <v>269.8160756060099</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>69.7745</v>
+        <v>59.59</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.7984392172359356</v>
+        <v>0.20732085686177</v>
       </c>
     </row>
     <row r="43">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>281.7691032345091</v>
+        <v>262.3078848992652</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>63.03627586206896</v>
+        <v>68.72016666666666</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.7905686327839871</v>
+        <v>0.052805140148848</v>
       </c>
     </row>
     <row r="44">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>276.8453909185047</v>
+        <v>247.2783550038311</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>64.18350000000001</v>
+        <v>48.9835</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.776754014824808</v>
+        <v>0.931343715637922</v>
       </c>
     </row>
     <row r="45">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>275.4887266615549</v>
+        <v>247.2713679110165</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>77.55850000000001</v>
+        <v>63.43266666666666</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.7729475782976949</v>
+        <v>0.090929493308067</v>
       </c>
     </row>
     <row r="46">
@@ -1638,22 +1638,22 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>275.1671597268749</v>
+        <v>246.5258087049245</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>64.22505172413793</v>
+        <v>55.91799999999999</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.772045347609588</v>
+        <v>0.28029961977154</v>
       </c>
     </row>
     <row r="47">
@@ -1662,22 +1662,22 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AO</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>273.1298257332056</v>
+        <v>242.3958530016534</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>75.15599999999999</v>
+        <v>62.1585</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.7663291341163045</v>
+        <v>0.102818396408111</v>
       </c>
     </row>
     <row r="48">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>270.6207893944373</v>
+        <v>240.9089796655124</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>71.194</v>
+        <v>73.10549999999999</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.7592894501865356</v>
+        <v>0.023442746896762</v>
       </c>
     </row>
     <row r="49">
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>269.958249039125</v>
+        <v>233.2588482042718</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>61.5415</v>
+        <v>59.0415</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.7574305394087006</v>
+        <v>0.14557873364538</v>
       </c>
     </row>
     <row r="50">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>269.2084412414758</v>
+        <v>231.9839293339342</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>57.7315</v>
+        <v>51.87</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.755326779561955</v>
+        <v>0.459332810714841</v>
       </c>
     </row>
     <row r="51">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>260.9244309650244</v>
+        <v>220.915991209458</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>74.10549999999999</v>
+        <v>70.7535</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.7320840655700949</v>
+        <v>0.024263313389383</v>
       </c>
     </row>
     <row r="52">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>252.5068130183221</v>
+        <v>219.6691082689652</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>72.06715517241379</v>
+        <v>67.80433333333335</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.7084664842418686</v>
+        <v>0.0349937035935</v>
       </c>
     </row>
     <row r="53">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>248.1632591918026</v>
+        <v>216.2594229977539</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>54.62</v>
+        <v>60.438</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.6962796356107138</v>
+        <v>0.094001408433542</v>
       </c>
     </row>
     <row r="54">
@@ -1830,22 +1830,22 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>BM</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>246.2681902302064</v>
+        <v>211.1140168503586</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>65.9085</v>
+        <v>69.11166666666666</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.6909625796922245</v>
+        <v>0.02615705889184</v>
       </c>
     </row>
     <row r="55">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>BM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>239.053413766377</v>
+        <v>209.3555343392073</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>71.34370689655172</v>
+        <v>68.0025</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.6707198493879564</v>
+        <v>0.029507296858355</v>
       </c>
     </row>
     <row r="56">
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>232.614359647574</v>
+        <v>207.5880500107877</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>69.02056896551724</v>
+        <v>72.8215</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.652653588209251</v>
+        <v>0.015533540863544</v>
       </c>
     </row>
     <row r="57">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>JO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>227.9627439956975</v>
+        <v>187.4092966470911</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>75.68600000000001</v>
+        <v>63.0835</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.6396024006094524</v>
+        <v>0.041603643330745</v>
       </c>
     </row>
     <row r="58">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>LK</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>226.0556579658053</v>
+        <v>185.0509329805859</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>61.90136206896551</v>
+        <v>76.4765</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.6342516280160552</v>
+        <v>0.007081443618517</v>
       </c>
     </row>
     <row r="59">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>224.244411418929</v>
+        <v>178.6501092853302</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>74.07550000000001</v>
+        <v>71.07550000000001</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.6291697553417223</v>
+        <v>0.012317726213951</v>
       </c>
     </row>
     <row r="60">
@@ -1974,22 +1974,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>215.5307285832831</v>
+        <v>173.3842437251963</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>65.77315517241379</v>
+        <v>60.52916666666666</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.6047214952350899</v>
+        <v>0.047791056567803</v>
       </c>
     </row>
     <row r="61">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>LK</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>200.0762588810476</v>
+        <v>159.3882323983299</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>76.4765</v>
+        <v>58.613</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.5613603926775489</v>
+        <v>0.049593322910368</v>
       </c>
     </row>
     <row r="62">
@@ -2022,22 +2022,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>196.3651531818365</v>
+        <v>157.3505721458322</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>63.36465517241379</v>
+        <v>48.79</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.5509480240925504</v>
+        <v>0.248672417365015</v>
       </c>
     </row>
     <row r="63">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BO</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>185.2969889160335</v>
+        <v>156.9701819725917</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52.54</v>
+        <v>75.59950000000001</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.5198937197327076</v>
+        <v>0.004794917913387</v>
       </c>
     </row>
     <row r="64">
@@ -2070,22 +2070,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>184.8612930324175</v>
+        <v>156.5955015101728</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>68.93049999999999</v>
+        <v>59.916</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.5186712737829356</v>
+        <v>0.038588023744524</v>
       </c>
     </row>
     <row r="65">
@@ -2094,22 +2094,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>178.7625927588364</v>
+        <v>155.6238357474494</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>65.31943103448276</v>
+        <v>64.93049999999999</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.501559954331308</v>
+        <v>0.018373403872829</v>
       </c>
     </row>
     <row r="66">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>172.7836730422892</v>
+        <v>147.8466153290485</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>61.113</v>
+        <v>51.6725</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.4847847070399042</v>
+        <v>0.123054895084351</v>
       </c>
     </row>
     <row r="67">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>172.5247150125232</v>
+        <v>142.5122411631637</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.3855</v>
+        <v>60.734</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.4840581401694048</v>
+        <v>0.025743615697138</v>
       </c>
     </row>
     <row r="68">
@@ -2166,22 +2166,22 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Isle of Man</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>IM</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>168.2580560212095</v>
+        <v>138.6091942595794</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>68.0855</v>
+        <v>47.4965</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.4720870378498184</v>
+        <v>0.216481927782297</v>
       </c>
     </row>
     <row r="69">
@@ -2190,22 +2190,22 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>163.3836631485658</v>
+        <v>133.4023965598298</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>62.95598275862069</v>
+        <v>50.79649999999999</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.4584107970386648</v>
+        <v>0.105435482691973</v>
       </c>
     </row>
     <row r="70">
@@ -2214,22 +2214,22 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>TZ</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>162.3331354620765</v>
+        <v>133.3320931966104</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>54.2965</v>
+        <v>69.413</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.4554632977306291</v>
+        <v>0.006336314982036</v>
       </c>
     </row>
     <row r="71">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>161.4242601619902</v>
+        <v>132.5446185857788</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>65.86113793103449</v>
+        <v>55.66233333333334</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.4529132370777323</v>
+        <v>0.045397676876746</v>
       </c>
     </row>
     <row r="72">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Isle of Man</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IM</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>157.8343656922856</v>
+        <v>132.5195105929949</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>48.26000000000001</v>
+        <v>64.8355</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.4428409547367152</v>
+        <v>0.011495389480842</v>
       </c>
     </row>
     <row r="73">
@@ -2286,22 +2286,22 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>157.141928036784</v>
+        <v>128.2153541691467</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>64.1335</v>
+        <v>74.93266666666666</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.4408981601424389</v>
+        <v>0.002829954246408</v>
       </c>
     </row>
     <row r="74">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>152.1695302944553</v>
+        <v>126.6509278726096</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>70.7895</v>
+        <v>70.88983333333334</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.426946943917219</v>
+        <v>0.004493342567002</v>
       </c>
     </row>
     <row r="75">
@@ -2334,22 +2334,22 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>151.4269330006053</v>
+        <v>126.6222516036076</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>62.416</v>
+        <v>69.50700000000001</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.4248634148128249</v>
+        <v>0.005361338116927</v>
       </c>
     </row>
     <row r="76">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>151.3621070792578</v>
+        <v>126.5129777773163</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>58.71477586206896</v>
+        <v>40.3855</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.4246815306409256</v>
+        <v>0.708559062331915</v>
       </c>
     </row>
     <row r="77">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>149.8909905435748</v>
+        <v>122.5415094421183</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>78.18125862068965</v>
+        <v>69.11199999999999</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.420553971675339</v>
+        <v>0.00511526959599</v>
       </c>
     </row>
     <row r="78">
@@ -2406,22 +2406,22 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>147.8674895655175</v>
+        <v>122.5384310362705</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>55.6878448275862</v>
+        <v>59.13350000000001</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.414876569918737</v>
+        <v>0.020812041475438</v>
       </c>
     </row>
     <row r="79">
@@ -2430,22 +2430,22 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>147.6809330040551</v>
+        <v>121.9745626118548</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>52.84491379310346</v>
+        <v>64.92866666666666</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.4143531421758114</v>
+        <v>0.008848699508234999</v>
       </c>
     </row>
     <row r="80">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>St. Kitts and Nevis</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>145.4503389583635</v>
+        <v>119.4002759260182</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>65.5055</v>
+        <v>76.31699999999999</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.4080946927405983</v>
+        <v>0.001938315108418</v>
       </c>
     </row>
     <row r="81">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>143.1731992328747</v>
+        <v>116.297563472572</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>49.9965</v>
+        <v>43.494</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.4017056485949757</v>
+        <v>0.282388948835433</v>
       </c>
     </row>
     <row r="82">
@@ -2502,22 +2502,22 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>139.0782581152906</v>
+        <v>114.9318963707564</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>49.1355</v>
+        <v>44.52233333333333</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.3902163406350285</v>
+        <v>0.220861728303134</v>
       </c>
     </row>
     <row r="83">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>137.537956875312</v>
+        <v>107.1141532435821</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>54.06699999999999</v>
+        <v>70.37966666666667</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.3858946679200755</v>
+        <v>0.002900786239479</v>
       </c>
     </row>
     <row r="84">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>St. Kitts and Nevis</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>129.6384273545551</v>
+        <v>106.5673496236328</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>78.09817241379309</v>
+        <v>45.3855</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.3637307039468364</v>
+        <v>0.148121593520045</v>
       </c>
     </row>
     <row r="85">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>129.3006710111673</v>
+        <v>104.4329965491802</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>47.13727586206896</v>
+        <v>49.6275</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.3627830501141736</v>
+        <v>0.062375154811889</v>
       </c>
     </row>
     <row r="86">
@@ -2598,22 +2598,22 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>TZ</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>126.4586146956108</v>
+        <v>103.7968056204527</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>67.538</v>
+        <v>60.7915</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.3548090013278002</v>
+        <v>0.009862027945928</v>
       </c>
     </row>
     <row r="87">
@@ -2622,22 +2622,22 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>126.1274278383585</v>
+        <v>101.8909417550307</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>71.91803448275861</v>
+        <v>64.98066666666666</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.3538797797136192</v>
+        <v>0.005120935020386</v>
       </c>
     </row>
     <row r="88">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>126.0967129919531</v>
+        <v>100.9390181945495</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>64.5415</v>
+        <v>54.4745</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.3537936020814722</v>
+        <v>0.02434657944832</v>
       </c>
     </row>
     <row r="89">
@@ -2670,22 +2670,22 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>125.2319519638685</v>
+        <v>100.2447581631243</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>76.91499999999999</v>
+        <v>46.317</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.351367314259955</v>
+        <v>0.10268836049363</v>
       </c>
     </row>
     <row r="90">
@@ -2694,22 +2694,22 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>116.7604935612851</v>
+        <v>98.61197601958118</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>72.3681724137931</v>
+        <v>62.67100000000001</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.3275986710335086</v>
+        <v>0.006429680070141</v>
       </c>
     </row>
     <row r="91">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>116.7300153898933</v>
+        <v>96.66175920274225</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>67.34201724137931</v>
+        <v>61.5055</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.3275131574480574</v>
+        <v>0.007170319440775</v>
       </c>
     </row>
     <row r="92">
@@ -2742,22 +2742,22 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>113.8151389208871</v>
+        <v>92.7984120523714</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>49.7495</v>
+        <v>72.166</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.3193347948157337</v>
+        <v>0.001505316868133</v>
       </c>
     </row>
     <row r="93">
@@ -2766,22 +2766,22 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>108.6833996882188</v>
+        <v>91.80761616731343</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>47.0475</v>
+        <v>66.7115</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.3049365090476947</v>
+        <v>0.002956853313663</v>
       </c>
     </row>
     <row r="94">
@@ -2790,22 +2790,22 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>99.87607033295104</v>
+        <v>91.01504788520828</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>75.691</v>
+        <v>62.36799999999999</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.2802255018899039</v>
+        <v>0.005280599725666</v>
       </c>
     </row>
     <row r="95">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>99.13987905028721</v>
+        <v>90.69948830350023</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>64.64349999999999</v>
+        <v>71.941</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.27815994633707</v>
+        <v>0.001445527232136</v>
       </c>
     </row>
     <row r="96">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>98.31365754803264</v>
+        <v>89.4679467482825</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>54.3335</v>
+        <v>52.32100000000001</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.2758417901023515</v>
+        <v>0.024373510677833</v>
       </c>
     </row>
     <row r="97">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Gibraltar</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>96.11533505741968</v>
+        <v>89.18726507599628</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>69.2115</v>
+        <v>46.2495</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.2696738860068633</v>
+        <v>0.073273200541735</v>
       </c>
     </row>
     <row r="98">
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>93.14565127558832</v>
+        <v>80.43962757452965</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>74.36427586206896</v>
+        <v>65.32283333333334</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.2613417487347038</v>
+        <v>0.002403394319117</v>
       </c>
     </row>
     <row r="99">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>91.44744768123064</v>
+        <v>77.61163388533349</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>54.0806724137931</v>
+        <v>49.5835</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.2565770443069695</v>
+        <v>0.025807495694608</v>
       </c>
     </row>
     <row r="100">
@@ -2934,22 +2934,22 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Anguilla</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>86.00335262468545</v>
+        <v>74.10224789915675</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>54.44863793103449</v>
+        <v>76.20349999999999</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.2413023717605727</v>
+        <v>0.000469591122965</v>
       </c>
     </row>
     <row r="101">
@@ -2958,22 +2958,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>84.23328404729963</v>
+        <v>71.25070502211456</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>50.84</v>
+        <v>50.838</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.2363360334392517</v>
+        <v>0.01594672066858</v>
       </c>
     </row>
     <row r="102">
@@ -2982,22 +2982,22 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>83.77842579519694</v>
+        <v>69.79168356693336</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>61.79600000000001</v>
+        <v>46.27</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.235059823016081</v>
+        <v>0.034971602144651</v>
       </c>
     </row>
     <row r="103">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>83.60663610678512</v>
+        <v>68.91860036559095</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>47.42749999999999</v>
+        <v>47.965</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.2345778271636788</v>
+        <v>0.02436067443341</v>
       </c>
     </row>
     <row r="104">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Anguilla</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>83.15429001057959</v>
+        <v>67.96028435599284</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>78.37806896551724</v>
+        <v>58.6615</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.2333086651770832</v>
+        <v>0.003815813033725</v>
       </c>
     </row>
     <row r="105">
@@ -3054,22 +3054,22 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>St. Lucia</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>82.0380353527313</v>
+        <v>67.80335478144269</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>50.55375862068966</v>
+        <v>68.413</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.2301767535921589</v>
+        <v>0.000949523746385</v>
       </c>
     </row>
     <row r="106">
@@ -3078,22 +3078,22 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FJ</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>80.54183721415212</v>
+        <v>64.26680335572935</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>50.4505</v>
+        <v>68.0055</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.2259788223668676</v>
+        <v>0.0008532253559680001</v>
       </c>
     </row>
     <row r="107">
@@ -3102,22 +3102,22 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>80.4130626290368</v>
+        <v>63.94816526638107</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>39.0315</v>
+        <v>44.164</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.2256175153728668</v>
+        <v>0.04091369046364</v>
       </c>
     </row>
     <row r="108">
@@ -3126,22 +3126,22 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>TC</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>79.58916274458583</v>
+        <v>62.33611021962317</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>48.7555</v>
+        <v>74.80466666666666</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.2233058729758678</v>
+        <v>0.000330263719661</v>
       </c>
     </row>
     <row r="109">
@@ -3150,22 +3150,22 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>78.92298404000631</v>
+        <v>62.24814493748968</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>67.53475862068964</v>
+        <v>39.2975</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.2214367539645086</v>
+        <v>0.107918260619044</v>
       </c>
     </row>
     <row r="110">
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>78.77431900396572</v>
+        <v>59.35907080773746</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>70.191</v>
+        <v>67.691</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.2210196396928009</v>
+        <v>0.000700943337506</v>
       </c>
     </row>
     <row r="111">
@@ -3198,22 +3198,22 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>77.50587435293534</v>
+        <v>58.39954323442767</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>52.338</v>
+        <v>44.489</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.2174607237505777</v>
+        <v>0.029171217465773</v>
       </c>
     </row>
     <row r="112">
@@ -3222,22 +3222,22 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>75.57014901874015</v>
+        <v>57.21248278798744</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>56.9245</v>
+        <v>45.863</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.2120295969402461</v>
+        <v>0.020859805226792</v>
       </c>
     </row>
     <row r="113">
@@ -3246,22 +3246,22 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>74.56800355082153</v>
+        <v>56.95911614202687</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>76.99360344827586</v>
+        <v>34.0315</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.2092178451785077</v>
+        <v>0.301828258670866</v>
       </c>
     </row>
     <row r="114">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>FJ</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>71.4761898319106</v>
+        <v>55.30256124719945</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>77.3805</v>
+        <v>53.84566666666667</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.2005430440149895</v>
+        <v>0.004445073136594</v>
       </c>
     </row>
     <row r="115">
@@ -3294,22 +3294,22 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>XK</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>71.04791278091348</v>
+        <v>54.76893429009933</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>64.39149999999999</v>
+        <v>50.862</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.1993414133224371</v>
+        <v>0.007212103810161</v>
       </c>
     </row>
     <row r="116">
@@ -3318,22 +3318,22 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>65.76808642136302</v>
+        <v>50.70919484033094</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>46.07850000000001</v>
+        <v>60.81916666666666</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.1845276347409981</v>
+        <v>0.001145238547906</v>
       </c>
     </row>
     <row r="117">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Cook Islands</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>CK</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>62.9222373979815</v>
+        <v>49.52071838361596</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>70.336</v>
+        <v>71.67749999999999</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.1765429446323317</v>
+        <v>0.000243172894443</v>
       </c>
     </row>
     <row r="118">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>59.84233372402561</v>
+        <v>48.9219801640523</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>70.34450000000001</v>
+        <v>41.496</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.1679015598648925</v>
+        <v>0.032096373615786</v>
       </c>
     </row>
     <row r="119">
@@ -3390,22 +3390,22 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>59.13966523921123</v>
+        <v>45.20822725912828</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>56.42899999999999</v>
+        <v>57.49149999999999</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.1659300603038574</v>
+        <v>0.001346541284875</v>
       </c>
     </row>
     <row r="120">
@@ -3414,22 +3414,22 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>St. Vincent &amp; Grenadines</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>57.94795836064428</v>
+        <v>43.87247864059933</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>64.58603448275861</v>
+        <v>63.70583333333334</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.1625864499972162</v>
+        <v>0.0004886115220869999</v>
       </c>
     </row>
     <row r="121">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>XK</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>57.45404347982244</v>
+        <v>42.20946032622029</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>44.48696551724138</v>
+        <v>61.89149999999999</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.1612006571350442</v>
+        <v>0.000564352330912</v>
       </c>
     </row>
     <row r="122">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>St. Lucia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>51.38779498506155</v>
+        <v>41.66100945295501</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>71.12072413793103</v>
+        <v>40.543</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1441803886826879</v>
+        <v>0.02443129196763</v>
       </c>
     </row>
     <row r="123">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>51.08473082700608</v>
+        <v>35.05270577416135</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>76.52965517241378</v>
+        <v>48.57083333333333</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.143330071829884</v>
+        <v>0.002862758083211</v>
       </c>
     </row>
     <row r="124">
@@ -3510,22 +3510,22 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>49.27184573327233</v>
+        <v>32.87191385093209</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>52.55862068965517</v>
+        <v>70.17733333333334</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.1382436018319484</v>
+        <v>8.604055779e-05</v>
       </c>
     </row>
     <row r="125">
@@ -3534,22 +3534,22 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>St. Vincent &amp; Grenadines</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>47.69220821696473</v>
+        <v>32.81624641809205</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>64.94860344827586</v>
+        <v>41.92516666666667</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.1338115620617034</v>
+        <v>0.008830667502480001</v>
       </c>
     </row>
     <row r="126">
@@ -3558,22 +3558,22 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>46.85175262360093</v>
+        <v>32.36456348354277</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>58.99149999999999</v>
+        <v>56.496</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1314534687798851</v>
+        <v>0.0005781625532109999</v>
       </c>
     </row>
     <row r="127">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>45.98816166641229</v>
+        <v>31.85420509587431</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>72.67693103448275</v>
+        <v>54.6585</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.1290304638639025</v>
+        <v>0.0007423025181200001</v>
       </c>
     </row>
     <row r="128">
@@ -3606,22 +3606,22 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>GU</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>42.27363228033142</v>
+        <v>31.17537448116421</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>59.545</v>
+        <v>67.316</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.1186084893305703</v>
+        <v>0.000106750599116</v>
       </c>
     </row>
     <row r="129">
@@ -3630,22 +3630,22 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>41.81764141176683</v>
+        <v>27.32972718861194</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>44.74772413793103</v>
+        <v>63.11900000000001</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.117329101088975</v>
+        <v>0.000128370402308</v>
       </c>
     </row>
     <row r="130">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>GU</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>41.20217127851308</v>
+        <v>26.14134468981402</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>70.066</v>
+        <v>69.2265</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1156022567466383</v>
+        <v>4.892517608800001e-05</v>
       </c>
     </row>
     <row r="131">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>39.31302527570477</v>
+        <v>23.15514256857703</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>61.1615</v>
+        <v>58.40266666666666</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.1103018190640635</v>
+        <v>0.000157053739258</v>
       </c>
     </row>
     <row r="132">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>American Samoa</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>36.74713676541259</v>
+        <v>21.24111433358903</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>55.9085</v>
+        <v>66.816</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.1031026231686585</v>
+        <v>3.6108349377e-05</v>
       </c>
     </row>
     <row r="133">
@@ -3726,22 +3726,22 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Nauru</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>30.96646821712624</v>
+        <v>18.19662715149842</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>71.54012068965518</v>
+        <v>53.10533333333334</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.08688361555449636</v>
+        <v>0.000179361586561</v>
       </c>
     </row>
     <row r="134">
@@ -3750,22 +3750,22 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>MV</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>28.34790369923254</v>
+        <v>15.29721557143547</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>59.61315517241379</v>
+        <v>61.96333333333333</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.07953662489085021</v>
+        <v>2.6584237389e-05</v>
       </c>
     </row>
     <row r="135">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Nauru</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>21.04732133816438</v>
+        <v>15.06739357541557</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>53.33251724137931</v>
+        <v>61.45983333333334</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.05905314622174651</v>
+        <v>2.7339589792e-05</v>
       </c>
     </row>
     <row r="136">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>MV</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>18.55218604703951</v>
+        <v>14.76936122212129</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>65.50984482758621</v>
+        <v>75.25666666666666</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.05205246490831682</v>
+        <v>4.160833456e-06</v>
       </c>
     </row>
     <row r="137">
@@ -3822,22 +3822,22 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>15.54040102723535</v>
+        <v>13.91635934261075</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>61.5015</v>
+        <v>69.09450000000001</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.0436022028390785</v>
+        <v>7.509060396e-06</v>
       </c>
     </row>
     <row r="138">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>13.99255243777174</v>
+        <v>12.14292204455001</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>29.142</v>
+        <v>69.086</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.03925935428300232</v>
+        <v>4.994122449e-06</v>
       </c>
     </row>
     <row r="139">
@@ -3879,13 +3879,13 @@
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>12.33476030830264</v>
+        <v>11.17558518887631</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>80.35808620689654</v>
+        <v>78.50966666666666</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.03460803360167246</v>
+        <v>1.231693414e-06</v>
       </c>
     </row>
     <row r="140">
@@ -3894,22 +3894,22 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>AO</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>7.659565338853624</v>
+        <v>10.60266837594453</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>69.066</v>
+        <v>72.90599999999999</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.02149068875240507</v>
+        <v>2.048217596e-06</v>
       </c>
     </row>
     <row r="141">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Cook Islands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>CK</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>3.729551913762887</v>
+        <v>8.782248052901137</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>71.60206896551725</v>
+        <v>25.142</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0.01046412372227517</v>
+        <v>0.016874025459401</v>
       </c>
     </row>
     <row r="142">
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="D142" s="5" t="n">
-        <v>2.319777905148269</v>
+        <v>5.81770244305531</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>70.70148275862068</v>
+        <v>68.50033333333333</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.006508675457256308</v>
+        <v>5.92953109e-07</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:10:22+00:00</t>
+          <t>2026-10-24T14:12:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:54+00:00</t>
+          <t>2026-10-24T15:23:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:23:34+00:00</t>
+          <t>2026-10-24T17:44:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:58+00:00</t>
+          <t>2026-10-24T21:21:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:21:35+00:00</t>
+          <t>2026-10-25T00:43:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:43:23+00:00</t>
+          <t>2026-10-25T07:58:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:58:11+00:00</t>
+          <t>2026-10-25T14:43:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:43:26+00:00</t>
+          <t>2026-10-25T18:01:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:01:18+00:00</t>
+          <t>2026-10-25T21:26:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:22+00:00</t>
+          <t>2026-10-26T00:57:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:57:41+00:00</t>
+          <t>2026-10-26T08:29:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:29:34+00:00</t>
+          <t>2026-10-26T17:05:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:05:46+00:00</t>
+          <t>2026-10-26T22:58:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:58:36+00:00</t>
+          <t>2026-10-27T01:45:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:45:25+00:00</t>
+          <t>2026-10-27T01:48:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:48:30+00:00</t>
+          <t>2026-10-27T08:32:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:32:28+00:00</t>
+          <t>2026-10-27T16:08:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:43+00:00</t>
+          <t>2026-10-27T22:47:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:47:32+00:00</t>
+          <t>2026-10-28T01:56:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:53+00:00</t>
+          <t>2026-10-28T09:11:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:11:58+00:00</t>
+          <t>2026-10-28T16:56:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:56:26+00:00</t>
+          <t>2026-10-28T22:56:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:56:15+00:00</t>
+          <t>2026-10-29T02:01:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:01:41+00:00</t>
+          <t>2026-10-29T06:41:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:41:52+00:00</t>
+          <t>2026-10-29T09:09:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:57+00:00</t>
+          <t>2026-10-29T17:13:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:58+00:00</t>
+          <t>2026-10-29T23:04:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:04:21+00:00</t>
+          <t>2026-10-30T02:17:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:17:35+00:00</t>
+          <t>2026-10-30T09:20:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:54+00:00</t>
+          <t>2026-10-30T16:55:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:55:10+00:00</t>
+          <t>2026-10-30T22:45:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/tjn-fsi.xlsx
+++ b/public/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:45:29+00:00</t>
+          <t>2026-10-31T01:56:47+00:00</t>
         </is>
       </c>
     </row>
